--- a/produtos import.xlsx
+++ b/produtos import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio-imagens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49AB790-7FBF-4E6E-9D0A-9FEF0D1CCA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADB5348-570F-4053-8F8E-168D76DCB0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C0354CA8-78AD-443A-AB4E-EFAC0043C03E}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="887">
   <si>
     <t>117.0002BL</t>
   </si>
@@ -2755,10 +2755,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3134,13 +3133,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE31CCE-98DC-414F-8C84-9EC50503832B}">
-  <dimension ref="A1:G416"/>
+  <dimension ref="A1:E416"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3157,7 +3156,7 @@
       <c r="D1" t="s">
         <v>886</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>884</v>
       </c>
     </row>
@@ -3688,7 +3687,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -3704,9 +3703,8 @@
       <c r="E33" t="s">
         <v>885</v>
       </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -3723,7 +3721,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>75</v>
       </c>
@@ -3740,7 +3738,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -3757,7 +3755,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -3774,7 +3772,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -3791,7 +3789,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -3808,7 +3806,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -3825,7 +3823,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -3842,7 +3840,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -3859,7 +3857,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -3876,7 +3874,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3893,7 +3891,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -3910,7 +3908,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>99</v>
       </c>
@@ -3927,7 +3925,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>101</v>
       </c>
@@ -3944,7 +3942,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
